--- a/08_third-party-ai-model-risk-assessment/exercises/solution/vendor_governance_solution.xlsx
+++ b/08_third-party-ai-model-risk-assessment/exercises/solution/vendor_governance_solution.xlsx
@@ -637,7 +637,7 @@
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Weights: Security 30%, Data Handling 25%, Transparency 20%, Financial Stability 15%, SLA 10%</t>
+          <t>Weights (example allocation across the 7 dimensions): Security 25%, Data Handling 20%, Transparency 15%, Financial Stability 10%, SLA Compliance 10%, Exit Strategy 10%, AI Model Governance 10%</t>
         </is>
       </c>
       <c r="B15" s="11" t="n"/>

--- a/08_third-party-ai-model-risk-assessment/exercises/solution/vendor_governance_solution.xlsx
+++ b/08_third-party-ai-model-risk-assessment/exercises/solution/vendor_governance_solution.xlsx
@@ -955,11 +955,15 @@
           <t>Limited</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>40</v>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>None published</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>

--- a/08_third-party-ai-model-risk-assessment/exercises/solution/vendor_governance_solution.xlsx
+++ b/08_third-party-ai-model-risk-assessment/exercises/solution/vendor_governance_solution.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>99.95%</t>
+          <t>99.75%</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
